--- a/crosswalk/FT3-F3-crosswalk.xlsx
+++ b/crosswalk/FT3-F3-crosswalk.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
   <si>
     <t>ft3_id</t>
   </si>
@@ -67,114 +67,90 @@
     <t>Gather Victim Org Information: Business Relationships</t>
   </si>
   <si>
-    <t>F1002.001</t>
-  </si>
-  <si>
-    <t>Abuse of Public-Facing API: Mobile API Abuse</t>
+    <t>FT004.002</t>
+  </si>
+  <si>
+    <t>Gather Victim Org Information: Determine Physical Locations </t>
+  </si>
+  <si>
+    <t>FT004.003</t>
+  </si>
+  <si>
+    <t>Gather Victim Org Information: Identify Business Tempo</t>
+  </si>
+  <si>
+    <t>FT004.004</t>
+  </si>
+  <si>
+    <t>Gather Victim Org Information: Identify Roles</t>
+  </si>
+  <si>
+    <t>FT005</t>
+  </si>
+  <si>
+    <t>Gather Victim Identity Information</t>
+  </si>
+  <si>
+    <t>FT005.001</t>
+  </si>
+  <si>
+    <t>Gather Victim Identity Information: Credentials</t>
+  </si>
+  <si>
+    <t>FT005.002</t>
+  </si>
+  <si>
+    <t>Gather Victim Identity Information: Email Addresses</t>
+  </si>
+  <si>
+    <t>FT005.003</t>
+  </si>
+  <si>
+    <t>Gather Victim Identity Information: Employee Names</t>
+  </si>
+  <si>
+    <t>FT006</t>
+  </si>
+  <si>
+    <t>Credential Scanning</t>
+  </si>
+  <si>
+    <t>FT006.001</t>
+  </si>
+  <si>
+    <t>Credential Scanning: Github</t>
+  </si>
+  <si>
+    <t>FT006.002</t>
+  </si>
+  <si>
+    <t>Credential Scanning: Websites</t>
+  </si>
+  <si>
+    <t>FT006.003</t>
+  </si>
+  <si>
+    <t>Credential Scanning: Telegram</t>
+  </si>
+  <si>
+    <t>FT007</t>
+  </si>
+  <si>
+    <t>Acquire Access</t>
+  </si>
+  <si>
+    <t>T1650</t>
+  </si>
+  <si>
+    <t>FT007.001</t>
+  </si>
+  <si>
+    <t>Acquire Access: Botnet</t>
   </si>
   <si>
     <t>derived</t>
   </si>
   <si>
-    <t>FT004.002</t>
-  </si>
-  <si>
-    <t>Gather Victim Org Information: Determine Physical Locations </t>
-  </si>
-  <si>
-    <t>F1002.002</t>
-  </si>
-  <si>
-    <t>Abuse of Public-Facing API: Web API Abuse</t>
-  </si>
-  <si>
-    <t>FT004.003</t>
-  </si>
-  <si>
-    <t>Gather Victim Org Information: Identify Business Tempo</t>
-  </si>
-  <si>
-    <t>F1005.003</t>
-  </si>
-  <si>
-    <t>Account Manipulation: Add Beneficiary</t>
-  </si>
-  <si>
-    <t>FT004.004</t>
-  </si>
-  <si>
-    <t>Gather Victim Org Information: Identify Roles</t>
-  </si>
-  <si>
-    <t>F1005.004</t>
-  </si>
-  <si>
-    <t>Account Manipulation: Change Account Details</t>
-  </si>
-  <si>
-    <t>FT005</t>
-  </si>
-  <si>
-    <t>Gather Victim Identity Information</t>
-  </si>
-  <si>
-    <t>FT005.001</t>
-  </si>
-  <si>
-    <t>Gather Victim Identity Information: Credentials</t>
-  </si>
-  <si>
-    <t>FT005.002</t>
-  </si>
-  <si>
-    <t>Gather Victim Identity Information: Email Addresses</t>
-  </si>
-  <si>
-    <t>FT005.003</t>
-  </si>
-  <si>
-    <t>Gather Victim Identity Information: Employee Names</t>
-  </si>
-  <si>
-    <t>FT006</t>
-  </si>
-  <si>
-    <t>Credential Scanning</t>
-  </si>
-  <si>
-    <t>FT006.001</t>
-  </si>
-  <si>
-    <t>Credential Scanning: Github</t>
-  </si>
-  <si>
-    <t>FT006.002</t>
-  </si>
-  <si>
-    <t>Credential Scanning: Websites</t>
-  </si>
-  <si>
-    <t>FT006.003</t>
-  </si>
-  <si>
-    <t>Credential Scanning: Telegram</t>
-  </si>
-  <si>
-    <t>FT007</t>
-  </si>
-  <si>
-    <t>Acquire Access</t>
-  </si>
-  <si>
-    <t>T1650</t>
-  </si>
-  <si>
-    <t>FT007.001</t>
-  </si>
-  <si>
-    <t>Acquire Access: Botnet</t>
-  </si>
-  <si>
     <t>FT007.002</t>
   </si>
   <si>
@@ -271,6 +247,15 @@
     <t>Compromise Infrastructure</t>
   </si>
   <si>
+    <t>T1583</t>
+  </si>
+  <si>
+    <t>Acquire Infrastructure</t>
+  </si>
+  <si>
+    <t>subset</t>
+  </si>
+  <si>
     <t>T1588</t>
   </si>
   <si>
@@ -367,6 +352,12 @@
     <t>Cross-Site Scripting (XSS) Redirection for Financial Fraud</t>
   </si>
   <si>
+    <t>F1007.003</t>
+  </si>
+  <si>
+    <t>Adversary-in-the-Browser: Malicious JavaScript Injection</t>
+  </si>
+  <si>
     <t>FT013</t>
   </si>
   <si>
@@ -421,6 +412,12 @@
     <t>Ad Fraud</t>
   </si>
   <si>
+    <t>T1583.008</t>
+  </si>
+  <si>
+    <t>Acquire Infrastructure: Malvertising</t>
+  </si>
+  <si>
     <t>FT018</t>
   </si>
   <si>
@@ -433,12 +430,24 @@
     <t>Website Cloning</t>
   </si>
   <si>
+    <t>F1020.002</t>
+  </si>
+  <si>
+    <t>Create Fake Materials: Fake Website</t>
+  </si>
+  <si>
     <t>FT020</t>
   </si>
   <si>
     <t>Identity Theft for Merchant Accounts</t>
   </si>
   <si>
+    <t>F1021</t>
+  </si>
+  <si>
+    <t>Create Fraudulent Merchant Account</t>
+  </si>
+  <si>
     <t>FT021</t>
   </si>
   <si>
@@ -466,6 +475,12 @@
     <t>Fabricating shipping evidence</t>
   </si>
   <si>
+    <t>F1020.001</t>
+  </si>
+  <si>
+    <t>Create Fake Materials: Fake Documents</t>
+  </si>
+  <si>
     <t>FT025</t>
   </si>
   <si>
@@ -478,6 +493,12 @@
     <t>Falsifying Business Documents</t>
   </si>
   <si>
+    <t>F1027</t>
+  </si>
+  <si>
+    <t>Falsify Business Documents</t>
+  </si>
+  <si>
     <t>FT026.001</t>
   </si>
   <si>
@@ -508,12 +529,6 @@
     <t>Falsifying Business Documents: Fake SS-4 Confirmation Letter</t>
   </si>
   <si>
-    <t>F1005.005</t>
-  </si>
-  <si>
-    <t>Account Manipulation: Change E-Delivery or Notification Settings</t>
-  </si>
-  <si>
     <t>FT027</t>
   </si>
   <si>
@@ -565,6 +580,12 @@
     <t>Compromised Payment Gateway</t>
   </si>
   <si>
+    <t>F1016</t>
+  </si>
+  <si>
+    <t>Compromise Payment Gateway</t>
+  </si>
+  <si>
     <t>FT032</t>
   </si>
   <si>
@@ -814,6 +835,12 @@
     <t>Fraudulent Purchases</t>
   </si>
   <si>
+    <t>F1028</t>
+  </si>
+  <si>
+    <t>Fradulent Purchasing</t>
+  </si>
+  <si>
     <t>FT051.001</t>
   </si>
   <si>
@@ -880,12 +907,6 @@
     <t>Falsifying Identity Documents: Fake Border Crossing Card</t>
   </si>
   <si>
-    <t>F1005.006</t>
-  </si>
-  <si>
-    <t>Account Manipulation: Change of Payment Details</t>
-  </si>
-  <si>
     <t>FT052.007</t>
   </si>
   <si>
@@ -896,12 +917,6 @@
   </si>
   <si>
     <t>Falsifying Identity Documents: Fake Passport Card</t>
-  </si>
-  <si>
-    <t>F1005.008</t>
-  </si>
-  <si>
-    <t>Account Manipulation: Update Call Receiving Device</t>
   </si>
   <si>
     <t>FT052.009</t>
@@ -1046,14 +1061,8 @@
       <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -1061,19 +1070,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -1081,19 +1084,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -1101,19 +1098,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -1121,10 +1112,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -1135,19 +1126,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -1155,19 +1140,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -1175,19 +1154,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -1195,10 +1168,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -1206,381 +1179,369 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>78</v>
+      </c>
+      <c r="C33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" t="s">
+        <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -1591,39 +1552,39 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F36" t="s">
         <v>8</v>
@@ -1631,56 +1592,56 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F37" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F38" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -1688,33 +1649,33 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -1722,67 +1683,67 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D42" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D45" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -1790,21 +1751,27 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>113</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" t="s">
+        <v>115</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E47" t="s">
         <v>12</v>
@@ -1812,30 +1779,30 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C48" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E49" t="s">
         <v>12</v>
@@ -1843,101 +1810,110 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D50" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E51" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F51" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D52" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F52" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E53" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F53" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" t="s">
         <v>135</v>
       </c>
-      <c r="B54" t="s">
-        <v>136</v>
-      </c>
       <c r="E54" t="s">
-        <v>12</v>
+        <v>81</v>
+      </c>
+      <c r="F54" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" t="s">
         <v>137</v>
-      </c>
-      <c r="B55" t="s">
-        <v>138</v>
       </c>
       <c r="E55" t="s">
         <v>12</v>
@@ -1945,32 +1921,44 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>138</v>
+      </c>
+      <c r="B56" t="s">
         <v>139</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>140</v>
       </c>
+      <c r="D56" t="s">
+        <v>141</v>
+      </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="C57" t="s">
+        <v>144</v>
+      </c>
+      <c r="D57" t="s">
+        <v>145</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E58" t="s">
         <v>12</v>
@@ -1978,16 +1966,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B59" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -1995,10 +1983,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E60" t="s">
         <v>12</v>
@@ -2006,21 +1994,27 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>154</v>
+      </c>
+      <c r="C61" t="s">
+        <v>155</v>
+      </c>
+      <c r="D61" t="s">
+        <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E62" t="s">
         <v>12</v>
@@ -2028,106 +2022,112 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>160</v>
+      </c>
+      <c r="C63" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" t="s">
+        <v>162</v>
       </c>
       <c r="E63" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="D64" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B66" t="s">
+        <v>168</v>
+      </c>
+      <c r="C66" t="s">
         <v>161</v>
       </c>
-      <c r="C66" t="s">
-        <v>28</v>
-      </c>
       <c r="D66" t="s">
-        <v>29</v>
+        <v>162</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>169</v>
+      </c>
+      <c r="B67" t="s">
+        <v>170</v>
+      </c>
+      <c r="C67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" t="s">
         <v>162</v>
       </c>
-      <c r="B67" t="s">
-        <v>163</v>
-      </c>
-      <c r="C67" t="s">
-        <v>32</v>
-      </c>
-      <c r="D67" t="s">
-        <v>33</v>
-      </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D68" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B69" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E69" t="s">
         <v>12</v>
@@ -2135,81 +2135,63 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
-      </c>
-      <c r="C70" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70" t="s">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B71" t="s">
-        <v>173</v>
-      </c>
-      <c r="C71" t="s">
-        <v>24</v>
-      </c>
-      <c r="D71" t="s">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B72" t="s">
-        <v>175</v>
-      </c>
-      <c r="C72" t="s">
-        <v>28</v>
-      </c>
-      <c r="D72" t="s">
-        <v>29</v>
+        <v>180</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B73" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D73" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F73" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B74" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E74" t="s">
         <v>12</v>
@@ -2217,16 +2199,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B75" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C75" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D75" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -2234,21 +2216,27 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B76" t="s">
-        <v>184</v>
+        <v>189</v>
+      </c>
+      <c r="C76" t="s">
+        <v>190</v>
+      </c>
+      <c r="D76" t="s">
+        <v>191</v>
       </c>
       <c r="E76" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E77" t="s">
         <v>12</v>
@@ -2256,27 +2244,27 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B78" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C78" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B79" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E79" t="s">
         <v>12</v>
@@ -2284,78 +2272,60 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B80" t="s">
-        <v>192</v>
-      </c>
-      <c r="C80" t="s">
-        <v>19</v>
-      </c>
-      <c r="D80" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B81" t="s">
-        <v>194</v>
-      </c>
-      <c r="C81" t="s">
-        <v>24</v>
-      </c>
-      <c r="D81" t="s">
-        <v>25</v>
+        <v>201</v>
       </c>
       <c r="E81" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B82" t="s">
-        <v>196</v>
-      </c>
-      <c r="C82" t="s">
-        <v>28</v>
-      </c>
-      <c r="D82" t="s">
-        <v>29</v>
+        <v>203</v>
       </c>
       <c r="E82" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B83" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C83" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="D83" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B84" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E84" t="s">
         <v>12</v>
@@ -2363,10 +2333,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E85" t="s">
         <v>12</v>
@@ -2374,10 +2344,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B86" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E86" t="s">
         <v>12</v>
@@ -2385,16 +2355,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B87" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C87" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D87" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -2402,61 +2372,61 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B88" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C88" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D88" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E88" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B89" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C89" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D89" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E89" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B90" t="s">
+        <v>219</v>
+      </c>
+      <c r="C90" t="s">
+        <v>213</v>
+      </c>
+      <c r="D90" t="s">
         <v>212</v>
       </c>
-      <c r="C90" t="s">
-        <v>206</v>
-      </c>
-      <c r="D90" t="s">
-        <v>205</v>
-      </c>
       <c r="E90" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B91" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E91" t="s">
         <v>12</v>
@@ -2464,78 +2434,54 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B92" t="s">
-        <v>216</v>
-      </c>
-      <c r="C92" t="s">
-        <v>19</v>
-      </c>
-      <c r="D92" t="s">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="E92" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B93" t="s">
-        <v>218</v>
-      </c>
-      <c r="C93" t="s">
-        <v>24</v>
-      </c>
-      <c r="D93" t="s">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="E93" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B94" t="s">
-        <v>220</v>
-      </c>
-      <c r="C94" t="s">
-        <v>28</v>
-      </c>
-      <c r="D94" t="s">
-        <v>29</v>
+        <v>227</v>
       </c>
       <c r="E94" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B95" t="s">
-        <v>222</v>
-      </c>
-      <c r="C95" t="s">
-        <v>32</v>
-      </c>
-      <c r="D95" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E95" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B96" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E96" t="s">
         <v>12</v>
@@ -2543,27 +2489,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B97" t="s">
-        <v>226</v>
-      </c>
-      <c r="C97" t="s">
-        <v>19</v>
-      </c>
-      <c r="D97" t="s">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="E97" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B98" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E98" t="s">
         <v>12</v>
@@ -2571,10 +2511,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B99" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E99" t="s">
         <v>12</v>
@@ -2582,16 +2522,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B100" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C100" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D100" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
@@ -2599,118 +2539,118 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B101" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C101" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D101" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E101" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B102" t="s">
+        <v>219</v>
+      </c>
+      <c r="C102" t="s">
+        <v>213</v>
+      </c>
+      <c r="D102" t="s">
         <v>212</v>
       </c>
-      <c r="C102" t="s">
-        <v>206</v>
-      </c>
-      <c r="D102" t="s">
-        <v>205</v>
-      </c>
       <c r="E102" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B103" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C103" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D103" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E103" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B104" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C104" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D104" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E104" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B105" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C105" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D105" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E105" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B106" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C106" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D106" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B107" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C107" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D107" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
@@ -2718,33 +2658,33 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B108" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C108" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E108" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B109" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C109" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D109" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -2752,10 +2692,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B110" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E110" t="s">
         <v>12</v>
@@ -2763,10 +2703,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B111" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="E111" t="s">
         <v>12</v>
@@ -2774,10 +2714,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E112" t="s">
         <v>12</v>
@@ -2785,10 +2725,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E113" t="s">
         <v>12</v>
@@ -2796,41 +2736,47 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B114" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C114" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
       </c>
       <c r="F114" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B115" t="s">
-        <v>263</v>
+        <v>270</v>
+      </c>
+      <c r="C115" t="s">
+        <v>144</v>
+      </c>
+      <c r="D115" t="s">
+        <v>145</v>
       </c>
       <c r="E115" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B116" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E116" t="s">
         <v>12</v>
@@ -2838,253 +2784,271 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B117" t="s">
-        <v>267</v>
+        <v>274</v>
+      </c>
+      <c r="C117" t="s">
+        <v>275</v>
+      </c>
+      <c r="D117" t="s">
+        <v>276</v>
       </c>
       <c r="E117" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B118" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C118" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="D118" t="s">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="E118" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B119" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C119" t="s">
-        <v>24</v>
+        <v>275</v>
       </c>
       <c r="D119" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
       <c r="E119" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B120" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>275</v>
       </c>
       <c r="D120" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="E120" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B121" t="s">
+        <v>284</v>
+      </c>
+      <c r="C121" t="s">
         <v>275</v>
       </c>
-      <c r="C121" t="s">
-        <v>32</v>
-      </c>
       <c r="D121" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="E121" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B122" t="s">
-        <v>277</v>
+        <v>286</v>
+      </c>
+      <c r="C122" t="s">
+        <v>155</v>
+      </c>
+      <c r="D122" t="s">
+        <v>156</v>
       </c>
       <c r="E122" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B123" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C123" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="D123" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E123" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B124" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C124" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="D124" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="E124" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B125" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C125" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="D125" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="E125" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B126" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C126" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="D126" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="E126" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B127" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C127" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D127" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E127" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B128" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C128" t="s">
-        <v>290</v>
+        <v>155</v>
       </c>
       <c r="D128" t="s">
-        <v>291</v>
+        <v>156</v>
       </c>
       <c r="E128" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B129" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C129" t="s">
-        <v>245</v>
+        <v>155</v>
       </c>
       <c r="D129" t="s">
-        <v>244</v>
+        <v>156</v>
       </c>
       <c r="E129" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B130" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C130" t="s">
-        <v>296</v>
+        <v>155</v>
       </c>
       <c r="D130" t="s">
-        <v>297</v>
+        <v>156</v>
       </c>
       <c r="E130" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B131" t="s">
-        <v>299</v>
+        <v>304</v>
+      </c>
+      <c r="C131" t="s">
+        <v>155</v>
+      </c>
+      <c r="D131" t="s">
+        <v>156</v>
       </c>
       <c r="E131" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B132" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C132" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D132" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E132" t="s">
         <v>9</v>
@@ -3092,32 +3056,44 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B133" t="s">
-        <v>304</v>
+        <v>309</v>
+      </c>
+      <c r="C133" t="s">
+        <v>140</v>
+      </c>
+      <c r="D133" t="s">
+        <v>141</v>
       </c>
       <c r="E133" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B134" t="s">
-        <v>306</v>
+        <v>311</v>
+      </c>
+      <c r="C134" t="s">
+        <v>140</v>
+      </c>
+      <c r="D134" t="s">
+        <v>141</v>
       </c>
       <c r="E134" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B135" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E135" t="s">
         <v>12</v>
@@ -3125,53 +3101,35 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B136" t="s">
-        <v>310</v>
-      </c>
-      <c r="C136" t="s">
-        <v>19</v>
-      </c>
-      <c r="D136" t="s">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="E136" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B137" t="s">
-        <v>312</v>
-      </c>
-      <c r="C137" t="s">
-        <v>24</v>
-      </c>
-      <c r="D137" t="s">
-        <v>25</v>
+        <v>317</v>
       </c>
       <c r="E137" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B138" t="s">
-        <v>314</v>
-      </c>
-      <c r="C138" t="s">
-        <v>28</v>
-      </c>
-      <c r="D138" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="E138" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/crosswalk/FT3-F3-crosswalk.xlsx
+++ b/crosswalk/FT3-F3-crosswalk.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
   <si>
     <t>ft3_id</t>
   </si>
@@ -148,7 +148,7 @@
     <t>Acquire Access: Botnet</t>
   </si>
   <si>
-    <t>derived</t>
+    <t>subset</t>
   </si>
   <si>
     <t>FT007.002</t>
@@ -253,9 +253,6 @@
     <t>Acquire Infrastructure</t>
   </si>
   <si>
-    <t>subset</t>
-  </si>
-  <si>
     <t>T1588</t>
   </si>
   <si>
@@ -310,6 +307,12 @@
     <t>Account Takeover: Exposed Credential</t>
   </si>
   <si>
+    <t>F1006.001</t>
+  </si>
+  <si>
+    <t>Account Takeover: Exposed API Key</t>
+  </si>
+  <si>
     <t>FT011.002</t>
   </si>
   <si>
@@ -664,6 +667,12 @@
     <t>Account Manipulation: Additional Authorized Account</t>
   </si>
   <si>
+    <t>F1005.002</t>
+  </si>
+  <si>
+    <t>Account Manipulation: Add Authorized User</t>
+  </si>
+  <si>
     <t>FT037.003</t>
   </si>
   <si>
@@ -733,7 +742,19 @@
     <t>Account Manipulation: Additional Payment Methods</t>
   </si>
   <si>
+    <t>F1005.006</t>
+  </si>
+  <si>
+    <t>Account Manipulation: Change of Payment Details</t>
+  </si>
+  <si>
     <t>FT042.002</t>
+  </si>
+  <si>
+    <t>F1005.001</t>
+  </si>
+  <si>
+    <t>Account Manipulation: Account Linking</t>
   </si>
   <si>
     <t>FT042.003</t>
@@ -1524,24 +1545,24 @@
         <v>80</v>
       </c>
       <c r="E33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" t="s">
         <v>81</v>
-      </c>
-      <c r="F33" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
         <v>83</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>84</v>
       </c>
-      <c r="C34" t="s">
-        <v>85</v>
-      </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -1552,36 +1573,36 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" t="s">
         <v>86</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" t="s">
         <v>87</v>
-      </c>
-      <c r="C35" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
         <v>89</v>
       </c>
-      <c r="B36" t="s">
-        <v>90</v>
-      </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
         <v>46</v>
@@ -1592,56 +1613,56 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
         <v>91</v>
       </c>
-      <c r="B37" t="s">
-        <v>92</v>
-      </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" t="s">
         <v>84</v>
-      </c>
-      <c r="E37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F37" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s">
         <v>93</v>
       </c>
-      <c r="B38" t="s">
-        <v>94</v>
-      </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" t="s">
         <v>84</v>
-      </c>
-      <c r="E38" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" t="s">
         <v>95</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>96</v>
       </c>
-      <c r="C39" t="s">
-        <v>97</v>
-      </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -1649,16 +1670,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" t="s">
         <v>98</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>99</v>
       </c>
-      <c r="C40" t="s">
-        <v>97</v>
-      </c>
       <c r="D40" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E40" t="s">
         <v>46</v>
@@ -1666,16 +1687,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" t="s">
         <v>102</v>
-      </c>
-      <c r="D41" t="s">
-        <v>101</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -1683,16 +1704,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E42" t="s">
         <v>46</v>
@@ -1700,16 +1721,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E43" t="s">
         <v>46</v>
@@ -1717,16 +1738,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E44" t="s">
         <v>46</v>
@@ -1734,16 +1755,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" t="s">
         <v>111</v>
-      </c>
-      <c r="D45" t="s">
-        <v>110</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -1751,16 +1772,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
@@ -1768,10 +1789,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E47" t="s">
         <v>12</v>
@@ -1779,30 +1800,30 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
+        <v>121</v>
+      </c>
+      <c r="D48" t="s">
         <v>120</v>
-      </c>
-      <c r="D48" t="s">
-        <v>119</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E49" t="s">
         <v>12</v>
@@ -1810,110 +1831,110 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" t="s">
         <v>125</v>
-      </c>
-      <c r="D50" t="s">
-        <v>124</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" t="s">
+        <v>128</v>
+      </c>
+      <c r="C51" t="s">
         <v>126</v>
       </c>
-      <c r="B51" t="s">
-        <v>127</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>125</v>
       </c>
-      <c r="D51" t="s">
-        <v>124</v>
-      </c>
       <c r="E51" t="s">
         <v>46</v>
       </c>
       <c r="F51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C52" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" t="s">
         <v>125</v>
       </c>
-      <c r="D52" t="s">
-        <v>124</v>
-      </c>
       <c r="E52" t="s">
         <v>46</v>
       </c>
       <c r="F52" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" t="s">
         <v>125</v>
       </c>
-      <c r="D53" t="s">
-        <v>124</v>
-      </c>
       <c r="E53" t="s">
         <v>46</v>
       </c>
       <c r="F53" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
+        <v>136</v>
+      </c>
+      <c r="E54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" t="s">
         <v>135</v>
-      </c>
-      <c r="E54" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E55" t="s">
         <v>12</v>
@@ -1921,16 +1942,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C56" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -1938,27 +1959,27 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E57" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
         <v>12</v>
@@ -1966,16 +1987,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C59" t="s">
+        <v>151</v>
+      </c>
+      <c r="D59" t="s">
         <v>150</v>
-      </c>
-      <c r="D59" t="s">
-        <v>149</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -1983,10 +2004,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E60" t="s">
         <v>12</v>
@@ -1994,27 +2015,27 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E61" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E62" t="s">
         <v>12</v>
@@ -2022,16 +2043,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D63" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
@@ -2039,95 +2060,95 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" t="s">
+        <v>165</v>
+      </c>
+      <c r="C64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" t="s">
         <v>163</v>
       </c>
-      <c r="B64" t="s">
-        <v>164</v>
-      </c>
-      <c r="C64" t="s">
-        <v>161</v>
-      </c>
-      <c r="D64" t="s">
-        <v>162</v>
-      </c>
       <c r="E64" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D65" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E65" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B66" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D66" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E66" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B67" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C67" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D67" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E67" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D68" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E68" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E69" t="s">
         <v>12</v>
@@ -2135,10 +2156,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B70" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E70" t="s">
         <v>12</v>
@@ -2146,10 +2167,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B71" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E71" t="s">
         <v>12</v>
@@ -2157,10 +2178,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E72" t="s">
         <v>12</v>
@@ -2168,30 +2189,30 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B73" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C73" t="s">
+        <v>126</v>
+      </c>
+      <c r="D73" t="s">
         <v>125</v>
       </c>
-      <c r="D73" t="s">
-        <v>124</v>
-      </c>
       <c r="E73" t="s">
         <v>46</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E74" t="s">
         <v>12</v>
@@ -2199,16 +2220,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B75" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C75" t="s">
+        <v>188</v>
+      </c>
+      <c r="D75" t="s">
         <v>187</v>
-      </c>
-      <c r="D75" t="s">
-        <v>186</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -2216,16 +2237,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B76" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C76" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -2233,10 +2254,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E77" t="s">
         <v>12</v>
@@ -2244,16 +2265,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B78" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D78" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -2261,10 +2282,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E79" t="s">
         <v>12</v>
@@ -2272,10 +2293,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E80" t="s">
         <v>12</v>
@@ -2283,10 +2304,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E81" t="s">
         <v>12</v>
@@ -2294,10 +2315,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B82" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E82" t="s">
         <v>12</v>
@@ -2305,27 +2326,27 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B83" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C83" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E83" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B84" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E84" t="s">
         <v>12</v>
@@ -2333,10 +2354,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E85" t="s">
         <v>12</v>
@@ -2344,10 +2365,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E86" t="s">
         <v>12</v>
@@ -2355,16 +2376,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B87" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C87" t="s">
+        <v>214</v>
+      </c>
+      <c r="D87" t="s">
         <v>213</v>
-      </c>
-      <c r="D87" t="s">
-        <v>212</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -2372,16 +2393,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>215</v>
+      </c>
+      <c r="B88" t="s">
+        <v>216</v>
+      </c>
+      <c r="C88" t="s">
         <v>214</v>
       </c>
-      <c r="B88" t="s">
-        <v>215</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>213</v>
-      </c>
-      <c r="D88" t="s">
-        <v>212</v>
       </c>
       <c r="E88" t="s">
         <v>46</v>
@@ -2389,16 +2410,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B89" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C89" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D89" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E89" t="s">
         <v>46</v>
@@ -2406,16 +2427,16 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B90" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C90" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" t="s">
         <v>213</v>
-      </c>
-      <c r="D90" t="s">
-        <v>212</v>
       </c>
       <c r="E90" t="s">
         <v>46</v>
@@ -2423,10 +2444,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B91" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E91" t="s">
         <v>12</v>
@@ -2434,10 +2455,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E92" t="s">
         <v>12</v>
@@ -2445,10 +2466,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E93" t="s">
         <v>12</v>
@@ -2456,10 +2477,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B94" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E94" t="s">
         <v>12</v>
@@ -2467,10 +2488,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B95" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E95" t="s">
         <v>12</v>
@@ -2478,10 +2499,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B96" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E96" t="s">
         <v>12</v>
@@ -2489,10 +2510,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B97" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
         <v>12</v>
@@ -2500,10 +2521,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B98" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E98" t="s">
         <v>12</v>
@@ -2511,10 +2532,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B99" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E99" t="s">
         <v>12</v>
@@ -2522,16 +2543,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
+        <v>214</v>
+      </c>
+      <c r="D100" t="s">
         <v>213</v>
-      </c>
-      <c r="D100" t="s">
-        <v>212</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
@@ -2539,16 +2560,16 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B101" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C101" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="D101" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="E101" t="s">
         <v>46</v>
@@ -2556,16 +2577,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C102" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="D102" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="E102" t="s">
         <v>46</v>
@@ -2573,16 +2594,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B103" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C103" t="s">
+        <v>214</v>
+      </c>
+      <c r="D103" t="s">
         <v>213</v>
-      </c>
-      <c r="D103" t="s">
-        <v>212</v>
       </c>
       <c r="E103" t="s">
         <v>46</v>
@@ -2590,16 +2611,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B104" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C104" t="s">
+        <v>214</v>
+      </c>
+      <c r="D104" t="s">
         <v>213</v>
-      </c>
-      <c r="D104" t="s">
-        <v>212</v>
       </c>
       <c r="E104" t="s">
         <v>46</v>
@@ -2607,16 +2628,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B105" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C105" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="D105" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="E105" t="s">
         <v>46</v>
@@ -2624,16 +2645,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
+        <v>255</v>
+      </c>
+      <c r="B106" t="s">
+        <v>256</v>
+      </c>
+      <c r="C106" t="s">
+        <v>247</v>
+      </c>
+      <c r="D106" t="s">
         <v>248</v>
-      </c>
-      <c r="B106" t="s">
-        <v>249</v>
-      </c>
-      <c r="C106" t="s">
-        <v>213</v>
-      </c>
-      <c r="D106" t="s">
-        <v>212</v>
       </c>
       <c r="E106" t="s">
         <v>46</v>
@@ -2641,16 +2662,16 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B107" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C107" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
@@ -2658,16 +2679,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B108" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C108" t="s">
+        <v>214</v>
+      </c>
+      <c r="D108" t="s">
         <v>213</v>
-      </c>
-      <c r="D108" t="s">
-        <v>212</v>
       </c>
       <c r="E108" t="s">
         <v>46</v>
@@ -2675,16 +2696,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B109" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C109" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -2692,10 +2713,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B110" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E110" t="s">
         <v>12</v>
@@ -2703,10 +2724,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B111" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E111" t="s">
         <v>12</v>
@@ -2714,10 +2735,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B112" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E112" t="s">
         <v>12</v>
@@ -2725,10 +2746,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B113" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E113" t="s">
         <v>12</v>
@@ -2736,36 +2757,36 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B114" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C114" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="D114" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
       </c>
       <c r="F114" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B115" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C115" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
@@ -2773,10 +2794,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B116" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E116" t="s">
         <v>12</v>
@@ -2784,16 +2805,16 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B117" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C117" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D117" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E117" t="s">
         <v>9</v>
@@ -2801,84 +2822,84 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B118" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C118" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D118" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E118" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B119" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C119" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D119" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E119" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B120" t="s">
+        <v>289</v>
+      </c>
+      <c r="C120" t="s">
         <v>282</v>
       </c>
-      <c r="C120" t="s">
-        <v>275</v>
-      </c>
       <c r="D120" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E120" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
+        <v>290</v>
+      </c>
+      <c r="B121" t="s">
+        <v>291</v>
+      </c>
+      <c r="C121" t="s">
+        <v>282</v>
+      </c>
+      <c r="D121" t="s">
         <v>283</v>
       </c>
-      <c r="B121" t="s">
-        <v>284</v>
-      </c>
-      <c r="C121" t="s">
-        <v>275</v>
-      </c>
-      <c r="D121" t="s">
-        <v>276</v>
-      </c>
       <c r="E121" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B122" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C122" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D122" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E122" t="s">
         <v>9</v>
@@ -2886,169 +2907,169 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B123" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C123" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D123" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E123" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B124" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C124" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D124" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E124" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B125" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C125" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D125" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E125" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B126" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C126" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D126" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E126" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B127" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C127" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D127" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E127" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B128" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C128" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D128" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E128" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B129" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C129" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D129" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E129" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B130" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C130" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D130" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E130" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B131" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C131" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D131" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E131" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B132" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C132" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D132" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="E132" t="s">
         <v>9</v>
@@ -3056,16 +3077,16 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B133" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C133" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D133" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E133" t="s">
         <v>9</v>
@@ -3073,27 +3094,27 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B134" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D134" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E134" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B135" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E135" t="s">
         <v>12</v>
@@ -3101,10 +3122,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B136" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="E136" t="s">
         <v>12</v>
@@ -3112,10 +3133,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B137" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E137" t="s">
         <v>12</v>
@@ -3123,10 +3144,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B138" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E138" t="s">
         <v>12</v>

--- a/crosswalk/FT3-F3-crosswalk.xlsx
+++ b/crosswalk/FT3-F3-crosswalk.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="337">
   <si>
     <t>ft3_id</t>
   </si>
@@ -406,6 +406,21 @@
     <t>Phishing: Backup Code</t>
   </si>
   <si>
+    <t>FT016.004</t>
+  </si>
+  <si>
+    <t>Phishing: Real-Time OTP Relay via Operator-Controlled Phishing Kit</t>
+  </si>
+  <si>
+    <t>T1111</t>
+  </si>
+  <si>
+    <t>Multi-Factor Authentication Interception</t>
+  </si>
+  <si>
+    <t>partial</t>
+  </si>
+  <si>
     <t>FT017</t>
   </si>
   <si>
@@ -529,6 +544,12 @@
     <t>Falsifying Business Documents: Fake SS-4 Confirmation Letter</t>
   </si>
   <si>
+    <t>FT026.006</t>
+  </si>
+  <si>
+    <t>Falsifying Business Documents: Live-Source Tax Certificate Forgery</t>
+  </si>
+  <si>
     <t>FT027</t>
   </si>
   <si>
@@ -968,6 +989,36 @@
   </si>
   <si>
     <t>Card Holder Details Collection: Card Details</t>
+  </si>
+  <si>
+    <t>FT057</t>
+  </si>
+  <si>
+    <t>Voice Phishing (Vishing)</t>
+  </si>
+  <si>
+    <t>F1040</t>
+  </si>
+  <si>
+    <t>Phone Number Spoofing</t>
+  </si>
+  <si>
+    <t>FT058</t>
+  </si>
+  <si>
+    <t>ClickFix Run-Dialog Social Engineering</t>
+  </si>
+  <si>
+    <t>FT059</t>
+  </si>
+  <si>
+    <t>Mobile Banking Trojan Distribution and Device Takeover</t>
+  </si>
+  <si>
+    <t>T1453</t>
+  </si>
+  <si>
+    <t>Abuse Accessibility Features</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1953,7 @@
         <v>135</v>
       </c>
       <c r="E54" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="F54" t="s">
         <v>134</v>
@@ -1910,162 +1961,165 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
+        <v>139</v>
+      </c>
+      <c r="D55" t="s">
+        <v>140</v>
       </c>
       <c r="E55" t="s">
-        <v>12</v>
+        <v>81</v>
+      </c>
+      <c r="F55" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
-      </c>
-      <c r="C56" t="s">
-        <v>140</v>
-      </c>
-      <c r="D56" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E56" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E57" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="C58" t="s">
+        <v>149</v>
+      </c>
+      <c r="D58" t="s">
+        <v>150</v>
       </c>
       <c r="E58" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
-      </c>
-      <c r="C59" t="s">
-        <v>150</v>
-      </c>
-      <c r="D59" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>154</v>
+      </c>
+      <c r="C60" t="s">
+        <v>155</v>
+      </c>
+      <c r="D60" t="s">
+        <v>154</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
-      </c>
-      <c r="C61" t="s">
-        <v>155</v>
-      </c>
-      <c r="D61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E61" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="C62" t="s">
+        <v>160</v>
+      </c>
+      <c r="D62" t="s">
+        <v>161</v>
       </c>
       <c r="E62" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
-      </c>
-      <c r="C63" t="s">
-        <v>161</v>
-      </c>
-      <c r="D63" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E63" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B64" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C64" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D64" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E64" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B65" t="s">
+        <v>169</v>
+      </c>
+      <c r="C65" t="s">
         <v>166</v>
       </c>
-      <c r="C65" t="s">
-        <v>161</v>
-      </c>
       <c r="D65" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E65" t="s">
         <v>81</v>
@@ -2073,16 +2127,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>170</v>
+      </c>
+      <c r="B66" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" t="s">
+        <v>166</v>
+      </c>
+      <c r="D66" t="s">
         <v>167</v>
-      </c>
-      <c r="B66" t="s">
-        <v>168</v>
-      </c>
-      <c r="C66" t="s">
-        <v>161</v>
-      </c>
-      <c r="D66" t="s">
-        <v>162</v>
       </c>
       <c r="E66" t="s">
         <v>81</v>
@@ -2090,16 +2144,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B67" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D67" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E67" t="s">
         <v>81</v>
@@ -2107,16 +2161,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C68" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D68" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E68" t="s">
         <v>81</v>
@@ -2124,32 +2178,44 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="C69" t="s">
+        <v>166</v>
+      </c>
+      <c r="D69" t="s">
+        <v>167</v>
       </c>
       <c r="E69" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B70" t="s">
-        <v>176</v>
+        <v>179</v>
+      </c>
+      <c r="C70" t="s">
+        <v>166</v>
+      </c>
+      <c r="D70" t="s">
+        <v>167</v>
       </c>
       <c r="E70" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B71" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E71" t="s">
         <v>12</v>
@@ -2157,10 +2223,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B72" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
         <v>12</v>
@@ -2168,30 +2234,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B73" t="s">
-        <v>182</v>
-      </c>
-      <c r="C73" t="s">
-        <v>125</v>
-      </c>
-      <c r="D73" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="E73" t="s">
-        <v>46</v>
-      </c>
-      <c r="F73" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E74" t="s">
         <v>12</v>
@@ -2199,36 +2256,33 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B75" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C75" t="s">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="D75" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="E75" t="s">
-        <v>9</v>
+        <v>46</v>
+      </c>
+      <c r="F75" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B76" t="s">
-        <v>189</v>
-      </c>
-      <c r="C76" t="s">
-        <v>190</v>
-      </c>
-      <c r="D76" t="s">
         <v>191</v>
       </c>
       <c r="E76" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
@@ -2238,22 +2292,28 @@
       <c r="B77" t="s">
         <v>193</v>
       </c>
+      <c r="C77" t="s">
+        <v>194</v>
+      </c>
+      <c r="D77" t="s">
+        <v>193</v>
+      </c>
       <c r="E77" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B78" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="D78" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -2261,10 +2321,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E79" t="s">
         <v>12</v>
@@ -2272,21 +2332,27 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B80" t="s">
-        <v>199</v>
+        <v>202</v>
+      </c>
+      <c r="C80" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" t="s">
+        <v>115</v>
       </c>
       <c r="E80" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E81" t="s">
         <v>12</v>
@@ -2294,10 +2360,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B82" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E82" t="s">
         <v>12</v>
@@ -2305,27 +2371,21 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B83" t="s">
-        <v>205</v>
-      </c>
-      <c r="C83" t="s">
-        <v>155</v>
-      </c>
-      <c r="D83" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="E83" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B84" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E84" t="s">
         <v>12</v>
@@ -2333,21 +2393,27 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>212</v>
+      </c>
+      <c r="C85" t="s">
+        <v>160</v>
+      </c>
+      <c r="D85" t="s">
+        <v>161</v>
       </c>
       <c r="E85" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B86" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E86" t="s">
         <v>12</v>
@@ -2355,67 +2421,55 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B87" t="s">
-        <v>212</v>
-      </c>
-      <c r="C87" t="s">
-        <v>213</v>
-      </c>
-      <c r="D87" t="s">
-        <v>212</v>
+        <v>157</v>
       </c>
       <c r="E87" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B88" t="s">
-        <v>215</v>
-      </c>
-      <c r="C88" t="s">
-        <v>213</v>
-      </c>
-      <c r="D88" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E88" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B89" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C89" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D89" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E89" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B90" t="s">
+        <v>222</v>
+      </c>
+      <c r="C90" t="s">
+        <v>220</v>
+      </c>
+      <c r="D90" t="s">
         <v>219</v>
-      </c>
-      <c r="C90" t="s">
-        <v>213</v>
-      </c>
-      <c r="D90" t="s">
-        <v>212</v>
       </c>
       <c r="E90" t="s">
         <v>46</v>
@@ -2423,32 +2477,44 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>223</v>
+      </c>
+      <c r="B91" t="s">
+        <v>224</v>
+      </c>
+      <c r="C91" t="s">
         <v>220</v>
       </c>
-      <c r="B91" t="s">
-        <v>221</v>
+      <c r="D91" t="s">
+        <v>219</v>
       </c>
       <c r="E91" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>226</v>
+      </c>
+      <c r="C92" t="s">
+        <v>220</v>
+      </c>
+      <c r="D92" t="s">
+        <v>219</v>
       </c>
       <c r="E92" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E93" t="s">
         <v>12</v>
@@ -2456,10 +2522,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B94" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E94" t="s">
         <v>12</v>
@@ -2467,10 +2533,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B95" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E95" t="s">
         <v>12</v>
@@ -2478,10 +2544,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B96" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E96" t="s">
         <v>12</v>
@@ -2489,10 +2555,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B97" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
         <v>12</v>
@@ -2500,10 +2566,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B98" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E98" t="s">
         <v>12</v>
@@ -2511,10 +2577,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B99" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E99" t="s">
         <v>12</v>
@@ -2522,67 +2588,55 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B100" t="s">
-        <v>212</v>
-      </c>
-      <c r="C100" t="s">
-        <v>213</v>
-      </c>
-      <c r="D100" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="E100" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B101" t="s">
-        <v>240</v>
-      </c>
-      <c r="C101" t="s">
-        <v>213</v>
-      </c>
-      <c r="D101" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="E101" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B102" t="s">
         <v>219</v>
       </c>
       <c r="C102" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D102" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E102" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B103" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C103" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D103" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E103" t="s">
         <v>46</v>
@@ -2590,16 +2644,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B104" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="C104" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D104" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E104" t="s">
         <v>46</v>
@@ -2607,16 +2661,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B105" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C105" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D105" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E105" t="s">
         <v>46</v>
@@ -2624,16 +2678,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B106" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C106" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D106" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E106" t="s">
         <v>46</v>
@@ -2641,33 +2695,33 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B107" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C107" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="D107" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="E107" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B108" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C108" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D108" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E108" t="s">
         <v>46</v>
@@ -2675,16 +2729,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B109" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C109" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -2692,32 +2746,44 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B110" t="s">
-        <v>259</v>
+        <v>261</v>
+      </c>
+      <c r="C110" t="s">
+        <v>220</v>
+      </c>
+      <c r="D110" t="s">
+        <v>219</v>
       </c>
       <c r="E110" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B111" t="s">
-        <v>261</v>
+        <v>263</v>
+      </c>
+      <c r="C111" t="s">
+        <v>264</v>
+      </c>
+      <c r="D111" t="s">
+        <v>263</v>
       </c>
       <c r="E111" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B112" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E112" t="s">
         <v>12</v>
@@ -2725,10 +2791,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B113" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E113" t="s">
         <v>12</v>
@@ -2736,64 +2802,58 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B114" t="s">
-        <v>267</v>
-      </c>
-      <c r="C114" t="s">
-        <v>268</v>
-      </c>
-      <c r="D114" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E114" t="s">
-        <v>9</v>
-      </c>
-      <c r="F114" t="s">
-        <v>268</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B115" t="s">
-        <v>270</v>
-      </c>
-      <c r="C115" t="s">
-        <v>144</v>
-      </c>
-      <c r="D115" t="s">
-        <v>145</v>
+        <v>272</v>
       </c>
       <c r="E115" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B116" t="s">
-        <v>272</v>
+        <v>274</v>
+      </c>
+      <c r="C116" t="s">
+        <v>275</v>
+      </c>
+      <c r="D116" t="s">
+        <v>274</v>
       </c>
       <c r="E116" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="F116" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B117" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C117" t="s">
-        <v>275</v>
+        <v>149</v>
       </c>
       <c r="D117" t="s">
-        <v>276</v>
+        <v>150</v>
       </c>
       <c r="E117" t="s">
         <v>9</v>
@@ -2801,50 +2861,44 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B118" t="s">
-        <v>278</v>
-      </c>
-      <c r="C118" t="s">
-        <v>275</v>
-      </c>
-      <c r="D118" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E118" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B119" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C119" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D119" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E119" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B120" t="s">
+        <v>285</v>
+      </c>
+      <c r="C120" t="s">
         <v>282</v>
       </c>
-      <c r="C120" t="s">
-        <v>275</v>
-      </c>
       <c r="D120" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E120" t="s">
         <v>81</v>
@@ -2852,16 +2906,16 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
+        <v>286</v>
+      </c>
+      <c r="B121" t="s">
+        <v>287</v>
+      </c>
+      <c r="C121" t="s">
+        <v>282</v>
+      </c>
+      <c r="D121" t="s">
         <v>283</v>
-      </c>
-      <c r="B121" t="s">
-        <v>284</v>
-      </c>
-      <c r="C121" t="s">
-        <v>275</v>
-      </c>
-      <c r="D121" t="s">
-        <v>276</v>
       </c>
       <c r="E121" t="s">
         <v>81</v>
@@ -2869,33 +2923,33 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B122" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C122" t="s">
-        <v>155</v>
+        <v>282</v>
       </c>
       <c r="D122" t="s">
-        <v>156</v>
+        <v>283</v>
       </c>
       <c r="E122" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B123" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C123" t="s">
-        <v>155</v>
+        <v>282</v>
       </c>
       <c r="D123" t="s">
-        <v>156</v>
+        <v>283</v>
       </c>
       <c r="E123" t="s">
         <v>81</v>
@@ -2903,33 +2957,33 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B124" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C124" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D124" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E124" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B125" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C125" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D125" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E125" t="s">
         <v>81</v>
@@ -2937,16 +2991,16 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B126" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C126" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D126" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E126" t="s">
         <v>81</v>
@@ -2954,16 +3008,16 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B127" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C127" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D127" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E127" t="s">
         <v>81</v>
@@ -2971,16 +3025,16 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B128" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C128" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D128" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E128" t="s">
         <v>81</v>
@@ -2988,16 +3042,16 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B129" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C129" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D129" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E129" t="s">
         <v>81</v>
@@ -3005,16 +3059,16 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B130" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C130" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D130" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E130" t="s">
         <v>81</v>
@@ -3022,16 +3076,16 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B131" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C131" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D131" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E131" t="s">
         <v>81</v>
@@ -3039,83 +3093,95 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B132" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C132" t="s">
-        <v>307</v>
+        <v>160</v>
       </c>
       <c r="D132" t="s">
-        <v>306</v>
+        <v>161</v>
       </c>
       <c r="E132" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B133" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C133" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D133" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="E133" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B134" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>314</v>
       </c>
       <c r="D134" t="s">
-        <v>141</v>
+        <v>313</v>
       </c>
       <c r="E134" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B135" t="s">
-        <v>313</v>
+        <v>316</v>
+      </c>
+      <c r="C135" t="s">
+        <v>145</v>
+      </c>
+      <c r="D135" t="s">
+        <v>146</v>
       </c>
       <c r="E135" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B136" t="s">
-        <v>315</v>
+        <v>318</v>
+      </c>
+      <c r="C136" t="s">
+        <v>145</v>
+      </c>
+      <c r="D136" t="s">
+        <v>146</v>
       </c>
       <c r="E136" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B137" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E137" t="s">
         <v>12</v>
@@ -3123,13 +3189,80 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B138" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E138" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>323</v>
+      </c>
+      <c r="B139" t="s">
+        <v>324</v>
+      </c>
+      <c r="E139" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>325</v>
+      </c>
+      <c r="B140" t="s">
+        <v>326</v>
+      </c>
+      <c r="E140" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>327</v>
+      </c>
+      <c r="B141" t="s">
+        <v>328</v>
+      </c>
+      <c r="C141" t="s">
+        <v>329</v>
+      </c>
+      <c r="D141" t="s">
+        <v>330</v>
+      </c>
+      <c r="E141" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>331</v>
+      </c>
+      <c r="B142" t="s">
+        <v>332</v>
+      </c>
+      <c r="E142" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>333</v>
+      </c>
+      <c r="B143" t="s">
+        <v>334</v>
+      </c>
+      <c r="C143" t="s">
+        <v>335</v>
+      </c>
+      <c r="D143" t="s">
+        <v>336</v>
+      </c>
+      <c r="E143" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/crosswalk/FT3-F3-crosswalk.xlsx
+++ b/crosswalk/FT3-F3-crosswalk.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
   <si>
     <t>ft3_id</t>
   </si>
@@ -1019,6 +1019,12 @@
   </si>
   <si>
     <t>Abuse Accessibility Features</t>
+  </si>
+  <si>
+    <t>FT060</t>
+  </si>
+  <si>
+    <t>Business Email Compromise</t>
   </si>
 </sst>
 </file>
@@ -3265,6 +3271,17 @@
         <v>136</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>337</v>
+      </c>
+      <c r="B144" t="s">
+        <v>338</v>
+      </c>
+      <c r="E144" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>